--- a/src/utils/sxsyzlzq/friends/xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16635" windowHeight="11700" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="72">
   <si>
     <t>名称</t>
   </si>
@@ -173,7 +173,7 @@
     <t>樱花·艾希尔</t>
   </si>
   <si>
-    <t>学仆观测型</t>
+    <t>学仆-观测型</t>
   </si>
   <si>
     <t>方尖魔碑</t>
@@ -246,9 +246,6 @@
   </si>
   <si>
     <t>黑金三代目·梅森</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
   </si>
   <si>
     <t>No.2时光·米拉</t>
@@ -1313,7 +1310,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1408,11 +1405,9 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1"/>
-    <row r="16" customFormat="1"/>
+        <v>16.8</v>
+      </c>
+    </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
         <v>15</v>
@@ -1424,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1505,10 +1500,10 @@
         <v>16</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1605,11 +1600,9 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2">
         <f>AVERAGE(D17:D28)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1"/>
-    <row r="33" customFormat="1"/>
+        <v>16.1666666666667</v>
+      </c>
+    </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
         <v>29</v>
@@ -1747,8 +1740,6 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
         <v>39</v>
@@ -1757,7 +1748,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D28,D34:D41)</f>
-        <v>15.9</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1984,8 +1975,6 @@
         <v>16.4166666666667</v>
       </c>
     </row>
-    <row r="17" customFormat="1"/>
-    <row r="18" customFormat="1"/>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>18</v>
@@ -2124,8 +2113,6 @@
         <v>16.125</v>
       </c>
     </row>
-    <row r="30" customFormat="1"/>
-    <row r="31" customFormat="1"/>
     <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
         <v>44</v>
@@ -2291,8 +2278,6 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
         <v>39</v>
@@ -2351,7 +2336,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2360,12 +2345,12 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2497,11 +2482,9 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1"/>
-    <row r="16" customFormat="1"/>
+        <v>16</v>
+      </c>
+    </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
         <v>15</v>
@@ -2513,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2597,7 +2580,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2707,11 +2690,9 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D17:D29)</f>
-        <v>15.3076923076923</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1"/>
-    <row r="34" customFormat="1"/>
+        <v>15.4615384615385</v>
+      </c>
+    </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
         <v>29</v>
@@ -2835,8 +2816,6 @@
         <v>14.8571428571429</v>
       </c>
     </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
         <v>39</v>
@@ -2845,7 +2824,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
     </row>
   </sheetData>
@@ -2895,7 +2874,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2904,12 +2883,12 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -3013,11 +2992,9 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.375</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1"/>
-    <row r="14" customFormat="1"/>
+        <v>15.5</v>
+      </c>
+    </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>18</v>
@@ -3255,8 +3232,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" customFormat="1"/>
-    <row r="34" customFormat="1"/>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
         <v>29</v>
@@ -3380,8 +3355,6 @@
         <v>14.8571428571429</v>
       </c>
     </row>
-    <row r="45" customFormat="1"/>
-    <row r="46" customFormat="1"/>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
         <v>39</v>
@@ -3390,7 +3363,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>14.5666666666667</v>
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>
@@ -3440,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3506,12 +3479,10 @@
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>17.3333333333333</v>
+        <v>17.5</v>
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" customFormat="1"/>
-    <row r="12" customFormat="1"/>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>15</v>
@@ -3520,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3575,7 +3546,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3630,11 +3601,9 @@
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C13:C21)</f>
-        <v>16.2222222222222</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1"/>
-    <row r="26" customFormat="1"/>
+        <v>16.4444444444444</v>
+      </c>
+    </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
         <v>60</v>
@@ -3723,8 +3692,6 @@
         <v>15.3333333333333</v>
       </c>
     </row>
-    <row r="36" customFormat="1"/>
-    <row r="37" customFormat="1"/>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
         <v>39</v>
@@ -3734,7 +3701,7 @@
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C7,C13:C21,C27:C32)</f>
-        <v>16.2857142857143</v>
+        <v>16.4285714285714</v>
       </c>
     </row>
   </sheetData>
@@ -3865,8 +3832,6 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" customFormat="1"/>
-    <row r="13" customFormat="1"/>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>19</v>
@@ -3933,8 +3898,6 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="21" customFormat="1"/>
-    <row r="22" customFormat="1"/>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
         <v>67</v>
@@ -4001,8 +3964,6 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="30" customFormat="1"/>
-    <row r="31" customFormat="1"/>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
         <v>39</v>
@@ -4045,7 +4006,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -4110,8 +4071,6 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="1"/>
-    <row r="10" customFormat="1"/>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>49</v>
@@ -4244,11 +4203,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="24" customFormat="1"/>
-    <row r="25" customFormat="1"/>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -4279,8 +4236,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" customFormat="1"/>
-    <row r="31" customFormat="1"/>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
         <v>39</v>

--- a/src/utils/sxsyzlzq/friends/xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -1670,7 +1670,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1737,7 +1737,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D34:D41)</f>
-        <v>14.75</v>
+        <v>14.875</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1748,7 +1748,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D28,D34:D41)</f>
-        <v>16</v>
+        <v>16.0333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2208,7 +2208,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2275,7 +2275,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D32:D41)</f>
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2286,7 +2286,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D13,D19:D26,D32:D41)</f>
-        <v>15.5666666666667</v>
+        <v>15.6</v>
       </c>
     </row>
   </sheetData>
@@ -2373,7 +2373,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2482,7 +2482,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>16</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2824,7 +2824,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>15.5</v>
+        <v>15.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2911,7 +2911,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2992,7 +2992,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.5</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3363,7 +3363,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>14.6</v>
+        <v>14.6333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3928,7 +3928,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>12.25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C8,C14:C17,C23:C26)</f>
-        <v>14.5333333333333</v>
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>
@@ -4023,7 +4023,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>12.9333333333333</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xk_level.xlsx
@@ -12,7 +12,7 @@
     <sheet name="伊萝莲" sheetId="3" r:id="rId3"/>
     <sheet name="阿斯塔拉" sheetId="4" r:id="rId4"/>
     <sheet name="帝国" sheetId="5" r:id="rId5"/>
-    <sheet name="海港" sheetId="6" r:id="rId6"/>
+    <sheet name="港口" sheetId="6" r:id="rId6"/>
     <sheet name="隐秘" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="70">
   <si>
     <t>名称</t>
   </si>
@@ -62,6 +62,9 @@
     <t>天使琼浆</t>
   </si>
   <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
     <t>圣殿弩手</t>
   </si>
   <si>
@@ -101,9 +104,6 @@
     <t>圣殿骑士</t>
   </si>
   <si>
-    <t>边境高墙</t>
-  </si>
-  <si>
     <t>海盗船长</t>
   </si>
   <si>
@@ -143,9 +143,6 @@
     <t>白袍·伊恩</t>
   </si>
   <si>
-    <t>黑道圣徒·梅森</t>
-  </si>
-  <si>
     <t>武圣·云长</t>
   </si>
   <si>
@@ -155,12 +152,12 @@
     <t>总计：</t>
   </si>
   <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
     <t>魔力风暴</t>
   </si>
   <si>
+    <t>黑旗舰队水手</t>
+  </si>
+  <si>
     <t>黑旗舰队飞斧手</t>
   </si>
   <si>
@@ -176,33 +173,33 @@
     <t>学仆-观测型</t>
   </si>
   <si>
+    <t>沉默否定</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
     <t>方尖魔碑</t>
   </si>
   <si>
-    <t>沉默否定</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
     <t>克隆术</t>
   </si>
   <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
     <t>缄言法师</t>
   </si>
   <si>
@@ -243,9 +240,6 @@
   </si>
   <si>
     <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>黑金三代目·梅森</t>
   </si>
   <si>
     <t>No.2时光·米拉</t>
@@ -1321,10 +1315,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1338,7 +1332,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1352,7 +1346,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1363,15 +1357,15 @@
         <v>5</v>
       </c>
       <c r="C10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
@@ -1380,14 +1374,22 @@
         <v>5</v>
       </c>
       <c r="D11" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1"/>
@@ -1396,44 +1398,36 @@
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <f>AVERAGE(D2:D11)</f>
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>15</v>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1">
+        <f>AVERAGE(D2:D12)</f>
+        <v>17.2727272727273</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1441,148 +1435,156 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2">
         <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3</v>
-      </c>
-      <c r="D21" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
         <v>4</v>
       </c>
       <c r="D26" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
-        <v>17</v>
-      </c>
-      <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>17</v>
+      </c>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="2">
         <v>6</v>
       </c>
-      <c r="D28" s="2">
-        <v>17</v>
-      </c>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="D29" s="2">
+        <v>17</v>
+      </c>
+      <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2"/>
@@ -1591,49 +1593,41 @@
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2">
-        <f>AVERAGE(D17:D28)</f>
-        <v>16.1666666666667</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="3">
-        <v>3</v>
-      </c>
-      <c r="D34" s="3">
-        <v>15</v>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2">
+        <f>AVERAGE(D18:D29)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C35" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>30</v>
@@ -1642,26 +1636,26 @@
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C37" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>30</v>
@@ -1670,40 +1664,40 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C40" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>30</v>
@@ -1729,26 +1723,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D34:D41)</f>
-        <v>14.875</v>
+        <f>AVERAGE(D35:D41)</f>
+        <v>15.5714285714286</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D11,D17:D28,D34:D41)</f>
-        <v>16.0333333333333</v>
+        <f>AVERAGE(D2:D12,D18:D29,D35:D41)</f>
+        <v>16.3666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1840,7 +1834,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1854,7 +1848,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -1863,12 +1857,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -1877,12 +1871,12 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -1891,12 +1885,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -1910,13 +1904,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="1">
         <v>15</v>
@@ -1924,21 +1918,21 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
@@ -1947,14 +1941,22 @@
         <v>5</v>
       </c>
       <c r="D13" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1"/>
@@ -1963,30 +1965,22 @@
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
-        <f>AVERAGE(D2:D13)</f>
-        <v>16.4166666666667</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2">
-        <v>18</v>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1">
+        <f>AVERAGE(D2:D14)</f>
+        <v>16.7692307692308</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1994,13 +1988,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2008,10 +2002,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
         <v>18</v>
@@ -2022,77 +2016,85 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="2">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
         <v>5</v>
       </c>
       <c r="D26" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
         <v>13</v>
       </c>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2"/>
@@ -2101,63 +2103,55 @@
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2">
-        <f>AVERAGE(D19:D26)</f>
-        <v>16.125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="3">
-        <v>2</v>
-      </c>
-      <c r="D32" s="3">
-        <v>13</v>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2">
+        <f>AVERAGE(D20:D27)</f>
+        <v>16.625</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C33" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C34" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>30</v>
@@ -2166,12 +2160,12 @@
         <v>4</v>
       </c>
       <c r="D35" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>30</v>
@@ -2180,26 +2174,26 @@
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C37" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>30</v>
@@ -2208,40 +2202,40 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C40" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>30</v>
@@ -2267,26 +2261,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D32:D41)</f>
-        <v>14.2</v>
+        <f>AVERAGE(D33:D41)</f>
+        <v>14.7777777777778</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D13,D19:D26,D32:D41)</f>
-        <v>15.6</v>
+        <f>AVERAGE(D2:D14,D20:D27,D33:D41)</f>
+        <v>16.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2350,7 +2344,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2359,12 +2353,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2373,18 +2367,18 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="1">
         <v>12</v>
@@ -2392,7 +2386,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -2401,12 +2395,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -2415,26 +2409,26 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2447,18 +2441,10 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1">
-        <v>16</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1"/>
@@ -2467,72 +2453,80 @@
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <f>AVERAGE(D2:D11)</f>
-        <v>16.1</v>
+      <c r="D13" s="1">
+        <f>AVERAGE(D2:D10)</f>
+        <v>16.8888888888889</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -2543,24 +2537,24 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -2571,16 +2565,16 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2588,7 +2582,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -2599,10 +2593,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
@@ -2616,7 +2610,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
         <v>5</v>
@@ -2627,10 +2621,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
@@ -2644,7 +2638,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2">
         <v>6</v>
@@ -2655,10 +2649,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2">
         <v>7</v>
@@ -2682,15 +2676,15 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
-        <f>AVERAGE(D17:D29)</f>
-        <v>15.4615384615385</v>
+        <f>AVERAGE(D16:D29)</f>
+        <v>15.1428571428571</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2704,7 +2698,7 @@
         <v>3</v>
       </c>
       <c r="D35" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2718,7 +2712,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2732,7 +2726,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2751,7 +2745,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>30</v>
@@ -2779,7 +2773,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>30</v>
@@ -2805,26 +2799,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>14.8571428571429</v>
+        <v>15.2857142857143</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>15.5333333333333</v>
+        <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
+        <v>15.7</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2882,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2897,12 +2891,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2916,7 +2910,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2930,7 +2924,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -2944,7 +2938,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -2958,7 +2952,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2967,7 +2961,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2984,37 +2978,37 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.625</v>
+        <v>15.875</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
@@ -3028,21 +3022,21 @@
         <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
@@ -3053,10 +3047,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -3067,10 +3061,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -3081,10 +3075,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -3098,21 +3092,21 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
         <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
         <v>4</v>
@@ -3123,10 +3117,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -3137,10 +3131,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
@@ -3154,7 +3148,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
         <v>5</v>
@@ -3165,10 +3159,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
@@ -3182,7 +3176,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2">
         <v>6</v>
@@ -3194,10 +3188,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2">
         <v>7</v>
@@ -3221,7 +3215,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>28</v>
@@ -3229,7 +3223,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D15:D29)</f>
-        <v>14</v>
+        <v>14.2666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3243,7 +3237,7 @@
         <v>3</v>
       </c>
       <c r="D35" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3257,7 +3251,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3271,7 +3265,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3290,7 +3284,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>30</v>
@@ -3318,7 +3312,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>30</v>
@@ -3344,26 +3338,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>14.8571428571429</v>
+        <v>15.2857142857143</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>14.6333333333333</v>
+        <v>14.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3418,29 +3412,29 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
@@ -3451,13 +3445,13 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3472,20 +3466,20 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>17.5</v>
+        <v>18.3333333333333</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -3496,13 +3490,13 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3510,21 +3504,21 @@
         <v>18</v>
       </c>
       <c r="B15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
         <v>20</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3535,7 +3529,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3594,52 +3588,52 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C13:C21)</f>
-        <v>16.4444444444444</v>
+        <v>16.1111111111111</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" s="3">
         <v>3</v>
       </c>
       <c r="C27" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" s="3">
         <v>4</v>
       </c>
       <c r="C28" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" s="3">
         <v>4</v>
       </c>
       <c r="C29" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" s="3">
         <v>5</v>
@@ -3650,7 +3644,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" s="3">
         <v>6</v>
@@ -3661,7 +3655,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="3">
         <v>8</v>
@@ -3682,26 +3676,26 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="3">
         <f>AVERAGE(C27:C32)</f>
-        <v>15.3333333333333</v>
+        <v>15.8333333333333</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C7,C13:C21,C27:C32)</f>
-        <v>16.4285714285714</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3767,7 +3761,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -3778,18 +3772,18 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -3800,86 +3794,92 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>15.7142857142857</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>17</v>
-      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>15.75</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -3887,59 +3887,53 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C14:C17)</f>
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>13</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C15:C18)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3954,26 +3948,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>12.5</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>12.3333333333333</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C17,C23:C26)</f>
-        <v>14.6</v>
+        <f>AVERAGE(C2:C9,C15:C18,C24:C26)</f>
+        <v>14.8666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4006,18 +4000,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -4028,7 +4022,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -4039,7 +4033,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -4060,20 +4054,20 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -4090,12 +4084,12 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -4106,7 +4100,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
@@ -4117,7 +4111,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -4128,7 +4122,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
@@ -4139,7 +4133,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -4150,7 +4144,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -4161,7 +4155,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -4172,7 +4166,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -4193,19 +4187,19 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -4226,10 +4220,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
@@ -4238,14 +4232,14 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>13</v>
+        <v>13.1333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xk_level.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="72">
   <si>
     <t>名称</t>
   </si>
@@ -242,7 +242,13 @@
     <t>钢之咆哮·布瑞恩</t>
   </si>
   <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
     <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1346,7 +1352,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1413,7 +1419,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1">
         <f>AVERAGE(D2:D12)</f>
-        <v>17.2727272727273</v>
+        <v>17.4545454545455</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1441,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1455,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1553,7 +1559,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1608,7 +1614,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D18:D29)</f>
-        <v>16</v>
+        <v>16.3333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1664,7 +1670,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1731,7 +1737,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.5714285714286</v>
+        <v>15.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1742,7 +1748,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D12,D18:D29,D35:D41)</f>
-        <v>16.3666666666667</v>
+        <v>16.6</v>
       </c>
     </row>
   </sheetData>
@@ -1787,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1871,7 +1877,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1980,7 +1986,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1">
         <f>AVERAGE(D2:D14)</f>
-        <v>16.7692307692308</v>
+        <v>16.9230769230769</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2064,7 +2070,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2118,7 +2124,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2">
         <f>AVERAGE(D20:D27)</f>
-        <v>16.625</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2202,7 +2208,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2269,7 +2275,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D33:D41)</f>
-        <v>14.7777777777778</v>
+        <v>14.8888888888889</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2280,7 +2286,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D14,D20:D27,D33:D41)</f>
-        <v>16.1333333333333</v>
+        <v>16.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2325,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2462,7 +2468,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <f>AVERAGE(D2:D10)</f>
-        <v>16.8888888888889</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2490,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2504,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2684,7 +2690,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D16:D29)</f>
-        <v>15.1428571428571</v>
+        <v>15.3571428571429</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2807,7 +2813,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.2857142857143</v>
+        <v>15.4285714285714</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2818,7 +2824,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>15.7</v>
+        <v>15.8666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2863,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2986,7 +2992,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>15.875</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3279,7 +3285,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3346,7 +3352,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.2857142857143</v>
+        <v>15.4285714285714</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3357,7 +3363,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>14.9333333333333</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3396,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3473,7 +3479,7 @@
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>18.3333333333333</v>
+        <v>18.5</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -3496,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3507,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3595,7 +3601,7 @@
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C13:C21)</f>
-        <v>16.1111111111111</v>
+        <v>16.4444444444444</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3639,7 +3645,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3683,7 +3689,7 @@
       </c>
       <c r="C35" s="3">
         <f>AVERAGE(C27:C32)</f>
-        <v>15.8333333333333</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -3695,7 +3701,7 @@
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C7,C13:C21,C27:C32)</f>
-        <v>16.6666666666667</v>
+        <v>16.9047619047619</v>
       </c>
     </row>
   </sheetData>
@@ -3778,7 +3784,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3833,7 +3839,7 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>15.75</v>
+        <v>15.875</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -3867,7 +3873,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3900,7 +3906,7 @@
       </c>
       <c r="C21" s="2">
         <f>AVERAGE(C15:C18)</f>
-        <v>15</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -3922,7 +3928,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3955,7 +3961,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C24:C26)</f>
-        <v>12.3333333333333</v>
+        <v>12.6666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3963,11 +3969,11 @@
         <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C9,C15:C18,C24:C26)</f>
-        <v>14.8666666666667</v>
+        <v>15.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4199,13 +4205,13 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4227,7 +4233,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -4235,11 +4241,11 @@
         <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>13.1333333333333</v>
+        <v>13.2</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -1712,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1737,7 +1737,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.7142857142857</v>
+        <v>15.8571428571429</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1748,7 +1748,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D12,D18:D29,D35:D41)</f>
-        <v>16.6</v>
+        <v>16.6333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2250,7 +2250,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2275,7 +2275,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D33:D41)</f>
-        <v>14.8888888888889</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2286,7 +2286,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D14,D20:D27,D33:D41)</f>
-        <v>16.2666666666667</v>
+        <v>16.3</v>
       </c>
     </row>
   </sheetData>
@@ -2788,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2813,7 +2813,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.4285714285714</v>
+        <v>15.5714285714286</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2824,7 +2824,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>15.8666666666667</v>
+        <v>15.9</v>
       </c>
     </row>
   </sheetData>
@@ -3327,7 +3327,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3352,7 +3352,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.4285714285714</v>
+        <v>15.5714285714286</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3363,7 +3363,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15</v>
+        <v>15.0333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3667,7 +3667,7 @@
         <v>8</v>
       </c>
       <c r="C32" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="C35" s="3">
         <f>AVERAGE(C27:C32)</f>
-        <v>16</v>
+        <v>16.1666666666667</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C7,C13:C21,C27:C32)</f>
-        <v>16.9047619047619</v>
+        <v>16.952380952381</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="71">
   <si>
     <t>名称</t>
   </si>
@@ -56,6 +56,9 @@
     <t>心灵黑洞</t>
   </si>
   <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
     <t>狡诈学徒</t>
   </si>
   <si>
@@ -83,15 +86,15 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
     <t>传记·钢铁守卫</t>
   </si>
   <si>
-    <t>紫色</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
     <t>圣殿御卫</t>
   </si>
   <si>
@@ -167,9 +170,6 @@
     <t>蒙面侠客·翔</t>
   </si>
   <si>
-    <t>樱花·艾希尔</t>
-  </si>
-  <si>
     <t>学仆-观测型</t>
   </si>
   <si>
@@ -234,9 +234,6 @@
   </si>
   <si>
     <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
   </si>
   <si>
     <t>钢之咆哮·布瑞恩</t>
@@ -1296,7 +1293,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1321,10 +1318,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1335,10 +1332,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1377,15 +1374,15 @@
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
@@ -1398,10 +1395,18 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1"/>
@@ -1410,66 +1415,58 @@
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
-        <f>AVERAGE(D2:D12)</f>
-        <v>17.4545454545455</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>15</v>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <f>AVERAGE(D2:D13)</f>
+        <v>17.6666666666667</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2">
         <v>2</v>
@@ -1480,10 +1477,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
@@ -1494,10 +1491,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -1508,10 +1505,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -1522,10 +1519,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
@@ -1536,10 +1533,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" s="2">
         <v>4</v>
@@ -1550,10 +1547,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2">
         <v>4</v>
@@ -1564,10 +1561,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="2">
         <v>5</v>
@@ -1579,10 +1576,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" s="2">
         <v>6</v>
@@ -1606,23 +1603,23 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
-        <f>AVERAGE(D18:D29)</f>
-        <v>16.3333333333333</v>
+        <f>AVERAGE(D19:D29)</f>
+        <v>16.7272727272727</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="3">
         <v>3</v>
@@ -1633,10 +1630,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="C36" s="3">
         <v>4</v>
@@ -1647,10 +1644,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" s="3">
         <v>4</v>
@@ -1661,10 +1658,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" s="3">
         <v>5</v>
@@ -1675,10 +1672,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C39" s="3">
         <v>5</v>
@@ -1689,10 +1686,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" s="3">
         <v>6</v>
@@ -1703,10 +1700,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C41" s="3">
         <v>8</v>
@@ -1729,10 +1726,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
@@ -1742,13 +1739,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D12,D18:D29,D35:D41)</f>
-        <v>16.6333333333333</v>
+        <f>AVERAGE(D2:D13,D19:D29,D35:D41)</f>
+        <v>16.9</v>
       </c>
     </row>
   </sheetData>
@@ -1826,21 +1823,21 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -1849,7 +1846,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1860,10 +1857,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1896,7 +1893,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -1905,7 +1902,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1919,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1930,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1">
         <v>15</v>
@@ -1938,21 +1935,21 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
@@ -1965,10 +1962,18 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1"/>
@@ -1977,30 +1982,22 @@
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
-        <f>AVERAGE(D2:D14)</f>
-        <v>16.9230769230769</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>20</v>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1">
+        <f>AVERAGE(D2:D15)</f>
+        <v>16.4285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2008,13 +2005,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2">
         <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2022,13 +2019,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2036,13 +2033,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2050,27 +2047,27 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
         <v>17</v>
-      </c>
-      <c r="C24" s="2">
-        <v>4</v>
-      </c>
-      <c r="D24" s="2">
-        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2078,35 +2075,43 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="2">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2">
         <v>17</v>
       </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="2">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
         <v>13</v>
       </c>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2"/>
@@ -2115,58 +2120,50 @@
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="2">
-        <f>AVERAGE(D20:D27)</f>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2">
+        <f>AVERAGE(D21:D28)</f>
         <v>16.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="3">
-        <v>2</v>
-      </c>
-      <c r="D33" s="3">
-        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C34" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="C35" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2174,35 +2171,35 @@
         <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C36" s="3">
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" s="3">
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" s="3">
         <v>5</v>
@@ -2213,10 +2210,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C39" s="3">
         <v>5</v>
@@ -2227,10 +2224,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" s="3">
         <v>6</v>
@@ -2241,10 +2238,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C41" s="3">
         <v>8</v>
@@ -2267,26 +2264,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D33:D41)</f>
-        <v>15</v>
+        <f>AVERAGE(D34:D41)</f>
+        <v>15.5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D14,D20:D27,D33:D41)</f>
-        <v>16.3</v>
+        <f>AVERAGE(D2:D15,D21:D28,D34:D41)</f>
+        <v>16.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2336,7 +2333,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2345,12 +2342,12 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2364,7 +2361,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2373,7 +2370,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2384,7 +2381,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1">
         <v>12</v>
@@ -2392,7 +2389,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -2401,12 +2398,12 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -2426,15 +2423,15 @@
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -2447,10 +2444,18 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1"/>
@@ -2459,66 +2464,58 @@
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
-        <f>AVERAGE(D2:D10)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>15</v>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
+        <f>AVERAGE(D2:D11)</f>
+        <v>17.3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
@@ -2532,7 +2529,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -2543,10 +2540,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -2557,10 +2554,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -2574,7 +2571,7 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -2585,10 +2582,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -2602,7 +2599,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
@@ -2613,10 +2610,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" s="2">
         <v>5</v>
@@ -2630,21 +2627,21 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
       </c>
       <c r="D27" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="2">
         <v>6</v>
@@ -2658,7 +2655,7 @@
         <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" s="2">
         <v>7</v>
@@ -2682,23 +2679,23 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
-        <f>AVERAGE(D16:D29)</f>
-        <v>15.3571428571429</v>
+        <f>AVERAGE(D17:D29)</f>
+        <v>15.6923076923077</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="3">
         <v>3</v>
@@ -2709,10 +2706,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="C36" s="3">
         <v>4</v>
@@ -2723,10 +2720,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" s="3">
         <v>4</v>
@@ -2737,10 +2734,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" s="3">
         <v>5</v>
@@ -2754,7 +2751,7 @@
         <v>52</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C39" s="3">
         <v>5</v>
@@ -2765,10 +2762,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" s="3">
         <v>6</v>
@@ -2779,10 +2776,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C41" s="3">
         <v>8</v>
@@ -2805,10 +2802,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
@@ -2818,13 +2815,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D10,D16:D29,D35:D41)</f>
-        <v>15.9</v>
+        <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>
@@ -2874,7 +2871,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2883,12 +2880,12 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2902,7 +2899,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2911,12 +2908,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2925,7 +2922,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2944,21 +2941,21 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2984,23 +2981,23 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>16</v>
+        <v>16.375</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
@@ -3014,7 +3011,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
@@ -3028,7 +3025,7 @@
         <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
@@ -3039,10 +3036,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
@@ -3056,7 +3053,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
@@ -3070,7 +3067,7 @@
         <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -3084,7 +3081,7 @@
         <v>56</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
@@ -3095,10 +3092,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2">
         <v>4</v>
@@ -3112,7 +3109,7 @@
         <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2">
         <v>4</v>
@@ -3126,7 +3123,7 @@
         <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
@@ -3140,7 +3137,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
@@ -3151,10 +3148,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" s="2">
         <v>5</v>
@@ -3168,21 +3165,21 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
       </c>
       <c r="D27" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="2">
         <v>6</v>
@@ -3197,7 +3194,7 @@
         <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" s="2">
         <v>7</v>
@@ -3221,23 +3218,23 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D15:D29)</f>
-        <v>14.2666666666667</v>
+        <v>14.3333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" s="3">
         <v>3</v>
@@ -3248,10 +3245,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="C36" s="3">
         <v>4</v>
@@ -3262,10 +3259,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" s="3">
         <v>4</v>
@@ -3276,10 +3273,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" s="3">
         <v>5</v>
@@ -3293,7 +3290,7 @@
         <v>52</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C39" s="3">
         <v>5</v>
@@ -3304,10 +3301,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" s="3">
         <v>6</v>
@@ -3318,10 +3315,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C41" s="3">
         <v>8</v>
@@ -3344,10 +3341,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
@@ -3357,13 +3354,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15.0333333333333</v>
+        <v>15.1666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3407,29 +3404,29 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -3443,15 +3440,15 @@
         <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
@@ -3461,64 +3458,64 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>18.5</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>15</v>
-      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>18.7142857142857</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2">
         <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -3529,7 +3526,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
@@ -3540,7 +3537,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
@@ -3551,7 +3548,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -3562,7 +3559,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -3573,7 +3570,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2">
         <v>6</v>
@@ -3594,14 +3591,14 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="2">
-        <f>AVERAGE(C13:C21)</f>
-        <v>16.4444444444444</v>
+        <f>AVERAGE(C14:C21)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3682,10 +3679,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3">
         <f>AVERAGE(C27:C32)</f>
@@ -3694,14 +3691,14 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C38" s="4">
-        <f>AVERAGE(C2:C7,C13:C21,C27:C32)</f>
-        <v>16.952380952381</v>
+        <f>AVERAGE(C2:C8,C14:C21,C27:C32)</f>
+        <v>17.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3756,46 +3753,46 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3806,7 +3803,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3814,83 +3811,89 @@
         <v>41</v>
       </c>
       <c r="B9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>15.875</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>18</v>
-      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>15.2222222222222</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2"/>
@@ -3898,42 +3901,36 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C15:C18)</f>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="2">
+        <f>AVERAGE(C16:C19)</f>
         <v>15.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -3954,26 +3951,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C24:C26)</f>
-        <v>12.6666666666667</v>
+        <f>AVERAGE(C25:C26)</f>
+        <v>13.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C18,C24:C26)</f>
-        <v>15.0666666666667</v>
+        <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4060,10 +4057,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
@@ -4167,7 +4164,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4193,19 +4190,19 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -4226,10 +4223,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C26:C26)</f>
@@ -4238,14 +4235,14 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>13.2</v>
+        <v>13.2666666666667</v>
       </c>
     </row>
   </sheetData>
